--- a/artfynd/S 470-2025 artfynd.xlsx
+++ b/artfynd/S 470-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AZ94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126490071</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95019824</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122245992</t>
         </is>
       </c>
     </row>
@@ -1106,6 +1126,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122599970</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122599452</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546331</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546302</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507079</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546300</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1723,6 +1773,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507054</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1820,6 +1875,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507076</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1917,6 +1977,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507089</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2014,6 +2079,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507075</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2111,6 +2181,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507052</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2208,6 +2283,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507078</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2305,6 +2385,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507064</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546148</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2503,6 +2593,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507073</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2600,6 +2695,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507059</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2707,6 +2807,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507062</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2827,6 +2932,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122599453</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2947,6 +3057,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122599686</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3078,6 +3193,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127968315</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3175,6 +3295,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507071</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3276,6 +3401,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544069</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3377,6 +3507,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544235</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3487,6 +3622,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544352</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3588,6 +3728,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544401</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3689,6 +3834,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544406</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3791,6 +3941,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3893,6 +4048,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/172131</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3995,6 +4155,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/172133</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4097,6 +4262,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57190144</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4194,6 +4364,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64315508</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4291,6 +4466,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64315510</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4388,6 +4568,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64963594</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4485,6 +4670,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76075925</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4586,6 +4776,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544363</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4687,6 +4882,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544365</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4788,6 +4988,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544334</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4889,6 +5094,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544336</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4990,6 +5200,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544337</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5091,6 +5306,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544058</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5188,6 +5408,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6917014</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5285,6 +5510,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6917015</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5386,6 +5616,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544230</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5487,6 +5722,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544297</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5588,6 +5828,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544012</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5689,6 +5934,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544013</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5786,6 +6036,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507070</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5887,6 +6142,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544488</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5988,6 +6248,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544494</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6085,6 +6350,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104619426</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6186,6 +6456,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544458</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6287,6 +6562,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544459</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6388,6 +6668,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546307</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6489,6 +6774,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544236</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6586,6 +6876,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15905533</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6683,6 +6978,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104619425</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6784,6 +7084,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544303</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6885,6 +7190,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544304</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6986,6 +7296,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544322</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7087,6 +7402,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546245</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7189,6 +7509,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1876119</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7291,6 +7616,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1876333</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7388,6 +7718,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64315509</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7485,6 +7820,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64315511</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7582,6 +7922,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64963595</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7679,6 +8024,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76075924</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7776,6 +8126,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104619351</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7873,6 +8228,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104619352</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7970,6 +8330,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104619353</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8067,6 +8432,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104619354</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8168,6 +8538,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544389</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8269,6 +8644,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544485</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8370,6 +8750,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122546333</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8472,6 +8857,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64315514</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8573,6 +8963,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544346</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8670,6 +9065,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122507085</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8771,6 +9171,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544043</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8878,6 +9283,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104619349</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8994,6 +9404,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15905529</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9101,6 +9516,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57190141</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9208,6 +9628,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64315513</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9315,6 +9740,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104619412</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9425,6 +9855,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544126</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9535,6 +9970,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544136</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9642,6 +10082,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15905528</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9749,6 +10194,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72060883</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9860,6 +10310,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15905530</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9961,6 +10416,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544323</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10076,6 +10536,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122599599</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10175,8 +10640,108 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70281643</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>